--- a/ReFalcon_R1.1(RC)_BOM.xlsx
+++ b/ReFalcon_R1.1(RC)_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Altium\ReFalcon030_GHR1\Project Outputs for ReFalcon030_R1.1(RC)\Git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD835E9E-547C-4168-BE31-C6F6B0D896B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254F5D13-698A-491A-8CA3-B0FEA6208BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{861E7B10-9DC4-4D57-A96C-BB46B26F2771}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="785">
   <si>
     <t>Manufacturer Part Number</t>
   </si>
@@ -2389,13 +2389,22 @@
   </si>
   <si>
     <t>Added alternate p/n for J6 SCSI connector</t>
+  </si>
+  <si>
+    <t>CAP CER 12PF 50V X8R 0805</t>
+  </si>
+  <si>
+    <t>CAP CER 47PF 50V C0G/NP0 0805</t>
+  </si>
+  <si>
+    <t>Corrected description for 12pF and 47pF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2407,6 +2416,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2479,7 +2495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -2490,6 +2506,8 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3899,8 +3917,8 @@
       <c r="B47" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>207</v>
+      <c r="C47" s="10" t="s">
+        <v>782</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>211</v>
@@ -4879,8 +4897,8 @@
       <c r="B90" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>381</v>
+      <c r="C90" s="10" t="s">
+        <v>783</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>385</v>
@@ -7030,7 +7048,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC48533-8B2C-4C15-8C82-0F6831306D07}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.53125" customWidth="1"/>
@@ -7078,6 +7096,15 @@
         <v>781</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B6" s="6">
+        <v>46272</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="11" t="s">
+        <v>784</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ReFalcon_R1.1(RC)_BOM.xlsx
+++ b/ReFalcon_R1.1(RC)_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254F5D13-698A-491A-8CA3-B0FEA6208BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5DFFBCB-E0E6-4ECA-A5E0-4A607E00028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{861E7B10-9DC4-4D57-A96C-BB46B26F2771}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="786">
   <si>
     <t>Manufacturer Part Number</t>
   </si>
@@ -1128,12 +1128,6 @@
     <t>2k</t>
   </si>
   <si>
-    <t>CFR-25JR-52-4K7</t>
-  </si>
-  <si>
-    <t>RES 4.7K OHM 5% 1/4W AXIAL</t>
-  </si>
-  <si>
     <t>R135</t>
   </si>
   <si>
@@ -2398,13 +2392,22 @@
   </si>
   <si>
     <t>Corrected description for 12pF and 47pF</t>
+  </si>
+  <si>
+    <t>RES 4.7 OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>CFR-25JR-52-4R7</t>
+  </si>
+  <si>
+    <t>Fixed typo in R135 description &amp; p/n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2423,6 +2426,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2495,7 +2504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -2507,7 +2516,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3910,27 +3923,27 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>782</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="C47" s="13" t="s">
+        <v>780</v>
+      </c>
+      <c r="D47" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="F47" s="1">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+      <c r="F47" s="14">
+        <v>1</v>
+      </c>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
@@ -4204,10 +4217,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.45">
@@ -4776,69 +4789,69 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A85" s="2" t="s">
+    <row r="85" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="D85" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C85" s="2" t="s">
+      <c r="E85" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F85" s="1">
-        <v>1</v>
-      </c>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
+      <c r="F85" s="11">
+        <v>1</v>
+      </c>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="F86" s="1">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="H86" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F86" s="1">
-        <v>1</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="E87" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="F87" s="1">
         <v>1</v>
@@ -4848,16 +4861,16 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>240</v>
@@ -4870,19 +4883,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="E89" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="F89" s="1">
         <v>3</v>
@@ -4890,43 +4903,43 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A90" s="2" t="s">
+    <row r="90" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>781</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="E90" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>783</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F90" s="1">
+      <c r="F90" s="14">
         <v>3</v>
       </c>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>242</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="F91" s="1">
         <v>1</v>
@@ -4936,19 +4949,19 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="D92" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
@@ -4958,19 +4971,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C93" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="F93" s="1">
         <v>1</v>
@@ -4980,43 +4993,43 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="E94" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="F94" s="1">
         <v>8</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C95" s="2" t="s">
+      <c r="E95" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="F95" s="1">
         <v>1</v>
@@ -5026,19 +5039,19 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="E96" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F96" s="1">
         <v>1</v>
@@ -5052,19 +5065,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
@@ -5074,45 +5087,45 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="E98" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F98" s="1">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="H98" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="F98" s="1">
-        <v>1</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="F99" s="1">
         <v>53</v>
@@ -5122,16 +5135,16 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="D100" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>87</v>
@@ -5144,19 +5157,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="E101" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="F101" s="1">
         <v>1</v>
@@ -5166,19 +5179,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="E102" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="F102" s="1">
         <v>1</v>
@@ -5188,16 +5201,16 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>49</v>
@@ -5214,19 +5227,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -5235,24 +5248,24 @@
         <v>38</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F105" s="1">
         <v>1</v>
@@ -5262,16 +5275,16 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="D106" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>209</v>
@@ -5284,45 +5297,45 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="D107" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="E107" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="F107" s="1">
         <v>2</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="E108" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F108" s="1">
         <v>3</v>
@@ -5332,19 +5345,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="E109" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="F109" s="1">
         <v>2</v>
@@ -5354,19 +5367,19 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="E110" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="F110" s="1">
         <v>2</v>
@@ -5376,19 +5389,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C111" s="2" t="s">
+      <c r="E111" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="F111" s="1">
         <v>1</v>
@@ -5398,19 +5411,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C112" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="F112" s="1">
         <v>1</v>
@@ -5419,24 +5432,24 @@
         <v>41</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C113" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="F113" s="1">
         <v>1</v>
@@ -5450,19 +5463,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C114" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
@@ -5472,45 +5485,45 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="D115" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="E115" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="F115" s="1">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="H115" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="F115" s="1">
-        <v>1</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C116" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="F116" s="1">
         <v>2</v>
@@ -5520,19 +5533,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="D117" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="E117" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
@@ -5541,24 +5554,24 @@
         <v>38</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C118" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="F118" s="1">
         <v>1</v>
@@ -5568,45 +5581,45 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="D119" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="E119" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="F119" s="1">
         <v>4</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C120" s="2" t="s">
+      <c r="E120" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -5616,19 +5629,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="D121" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="E121" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>533</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
@@ -5638,19 +5651,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="C122" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="F122" s="1">
         <v>2</v>
@@ -5660,19 +5673,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
@@ -5682,19 +5695,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="F124" s="1">
         <v>5</v>
@@ -5704,19 +5717,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>242</v>
       </c>
       <c r="C125" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
@@ -5725,24 +5738,24 @@
         <v>38</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F126" s="1">
         <v>1</v>
@@ -5751,24 +5764,24 @@
         <v>199</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -5777,24 +5790,24 @@
         <v>199</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="E128" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="F128" s="1">
         <v>1</v>
@@ -5808,19 +5821,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C129" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="F129" s="1">
         <v>2</v>
@@ -5830,45 +5843,45 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="D130" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="E130" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F130" s="1">
+        <v>1</v>
+      </c>
+      <c r="G130" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="H130" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="F130" s="1">
-        <v>1</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C131" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="F131" s="1">
         <v>1</v>
@@ -5878,19 +5891,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C132" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="F132" s="1">
         <v>1</v>
@@ -5900,19 +5913,19 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C133" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="F133" s="1">
         <v>2</v>
@@ -5922,19 +5935,19 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C134" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="F134" s="1">
         <v>15</v>
@@ -5944,16 +5957,16 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>133</v>
@@ -5966,19 +5979,19 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C136" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="F136" s="1">
         <v>28</v>
@@ -5988,19 +6001,19 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C137" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="F137" s="1">
         <v>16</v>
@@ -6010,16 +6023,16 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="D138" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>117</v>
@@ -6032,19 +6045,19 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C139" s="2" t="s">
+      <c r="E139" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="F139" s="1">
         <v>1</v>
@@ -6054,19 +6067,19 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C140" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="F140" s="1">
         <v>15</v>
@@ -6076,19 +6089,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C141" s="2" t="s">
+      <c r="E141" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="F141" s="1">
         <v>4</v>
@@ -6098,19 +6111,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C142" s="2" t="s">
+      <c r="E142" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="F142" s="1">
         <v>3</v>
@@ -6120,19 +6133,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C143" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>620</v>
       </c>
       <c r="F143" s="1">
         <v>7</v>
@@ -6142,19 +6155,19 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C144" s="2" t="s">
+      <c r="E144" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="F144" s="1">
         <v>4</v>
@@ -6164,19 +6177,19 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C145" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E145" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="F145" s="1">
         <v>1</v>
@@ -6186,19 +6199,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D146" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C146" s="2" t="s">
+      <c r="E146" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="F146" s="1">
         <v>3</v>
@@ -6208,16 +6221,16 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D147" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>117</v>
@@ -6230,19 +6243,19 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="D148" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="E148" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F148" s="1">
         <v>1</v>
@@ -6252,19 +6265,19 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C149" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="F149" s="1">
         <v>4</v>
@@ -6274,19 +6287,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F150" s="1">
         <v>1</v>
@@ -6296,19 +6309,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C151" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="F151" s="1">
         <v>2</v>
@@ -6318,16 +6331,16 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>125</v>
@@ -6340,16 +6353,16 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>117</v>
@@ -6362,19 +6375,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C154" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="F154" s="1">
         <v>1</v>
@@ -6384,19 +6397,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C155" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="F155" s="1">
         <v>2</v>
@@ -6406,19 +6419,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C156" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E156" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="F156" s="1">
         <v>2</v>
@@ -6428,16 +6441,16 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>129</v>
@@ -6450,19 +6463,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A158" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C158" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E158" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="F158" s="1">
         <v>1</v>
@@ -6472,19 +6485,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C159" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>677</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="F159" s="1">
         <v>1</v>
@@ -6494,19 +6507,19 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A160" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C160" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="F160" s="1">
         <v>4</v>
@@ -6516,16 +6529,16 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A161" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>121</v>
@@ -6538,19 +6551,19 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A162" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C162" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>690</v>
       </c>
       <c r="F162" s="1">
         <v>2</v>
@@ -6560,19 +6573,19 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A163" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C163" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="F163" s="1">
         <v>2</v>
@@ -6582,19 +6595,19 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A164" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C164" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="F164" s="1">
         <v>1</v>
@@ -6604,19 +6617,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A165" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C165" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="F165" s="1">
         <v>2</v>
@@ -6626,19 +6639,19 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F166" s="1">
         <v>1</v>
@@ -6648,19 +6661,19 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A167" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C167" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>707</v>
       </c>
       <c r="F167" s="1">
         <v>1</v>
@@ -6670,19 +6683,19 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A168" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F168" s="1">
         <v>12</v>
@@ -6692,19 +6705,19 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A169" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="D169" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="E169" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>715</v>
       </c>
       <c r="F169" s="1">
         <v>1</v>
@@ -6713,24 +6726,24 @@
         <v>161</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A170" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C170" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="F170" s="1">
         <v>1</v>
@@ -6739,24 +6752,24 @@
         <v>186</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A171" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="D171" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="E171" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="F171" s="1">
         <v>2</v>
@@ -6766,19 +6779,19 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A172" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C172" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E172" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="F172" s="1">
         <v>1</v>
@@ -6788,19 +6801,19 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A173" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C173" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>733</v>
       </c>
       <c r="F173" s="1">
         <v>1</v>
@@ -6810,19 +6823,19 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A174" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C174" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="F174" s="1">
         <v>1</v>
@@ -6832,19 +6845,19 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A175" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F175" s="1">
         <v>4</v>
@@ -6854,19 +6867,19 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A176" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C176" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E176" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="F176" s="1">
         <v>1</v>
@@ -6876,19 +6889,19 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A177" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F177" s="1">
         <v>1</v>
@@ -6898,19 +6911,19 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A178" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F178" s="1">
         <v>1</v>
@@ -6920,19 +6933,19 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A179" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="F179" s="1">
         <v>2</v>
@@ -6941,21 +6954,21 @@
         <v>38</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A180" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>356</v>
@@ -6968,19 +6981,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A181" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="D181" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="C181" s="2" t="s">
+      <c r="E181" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="F181" s="1">
         <v>1</v>
@@ -6989,24 +7002,24 @@
         <v>38</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A182" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="D182" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="E182" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>768</v>
       </c>
       <c r="F182" s="1">
         <v>1</v>
@@ -7020,19 +7033,19 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A183" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="D183" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="C183" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>772</v>
-      </c>
       <c r="E183" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="F183" s="1">
         <v>1</v>
@@ -7048,7 +7061,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDC48533-8B2C-4C15-8C82-0F6831306D07}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.53125" customWidth="1"/>
@@ -7057,16 +7070,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B2" s="5" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -7074,10 +7087,10 @@
         <v>46242</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
@@ -7086,14 +7099,14 @@
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -7101,8 +7114,17 @@
         <v>46272</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="11" t="s">
-        <v>784</v>
+      <c r="D6" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="6">
+        <v>46287</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
